--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/57.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/57.xlsx
@@ -426,13 +426,13 @@
         <v>-8.51712683328336</v>
       </c>
       <c r="E2">
-        <v>-18.40067278087277</v>
+        <v>-29.8576644713017</v>
       </c>
       <c r="F2">
-        <v>-5.286150518411495</v>
+        <v>-5.628219867193135</v>
       </c>
       <c r="G2">
-        <v>-12.67373615429591</v>
+        <v>-18.55326337676876</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.658253371738528</v>
       </c>
       <c r="E3">
-        <v>-19.64536914662105</v>
+        <v>-30.05196996978581</v>
       </c>
       <c r="F3">
-        <v>-5.015015927066384</v>
+        <v>-5.618673761243273</v>
       </c>
       <c r="G3">
-        <v>-13.34614105877728</v>
+        <v>-19.28526472204809</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.734531297380784</v>
       </c>
       <c r="E4">
-        <v>-18.83616706924241</v>
+        <v>-29.54508428868525</v>
       </c>
       <c r="F4">
-        <v>-5.150581566004134</v>
+        <v>-5.685886663939022</v>
       </c>
       <c r="G4">
-        <v>-12.93020411722324</v>
+        <v>-19.2433979078857</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.732714818133728</v>
       </c>
       <c r="E5">
-        <v>-19.8062794135356</v>
+        <v>-31.07918863555272</v>
       </c>
       <c r="F5">
-        <v>-5.069153050308943</v>
+        <v>-5.681473950784309</v>
       </c>
       <c r="G5">
-        <v>-13.48361146229551</v>
+        <v>-19.12277156007128</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.653823244962727</v>
       </c>
       <c r="E6">
-        <v>-20.65652757931975</v>
+        <v>-30.48063984782589</v>
       </c>
       <c r="F6">
-        <v>-5.142015418691784</v>
+        <v>-5.596655755676862</v>
       </c>
       <c r="G6">
-        <v>-12.14155602722144</v>
+        <v>-19.06541966914894</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.496213250535799</v>
       </c>
       <c r="E7">
-        <v>-21.4048669660353</v>
+        <v>-31.35685201933303</v>
       </c>
       <c r="F7">
-        <v>-5.200725958365199</v>
+        <v>-5.496028168686986</v>
       </c>
       <c r="G7">
-        <v>-12.4824429014002</v>
+        <v>-19.17531653887059</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.262095818208833</v>
       </c>
       <c r="E8">
-        <v>-20.47103675549157</v>
+        <v>-32.14790850136293</v>
       </c>
       <c r="F8">
-        <v>-4.881694335422817</v>
+        <v>-5.452298653493201</v>
       </c>
       <c r="G8">
-        <v>-12.43176507028504</v>
+        <v>-18.22895240410514</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.954873192913311</v>
       </c>
       <c r="E9">
-        <v>-21.06006442661727</v>
+        <v>-32.59949019364482</v>
       </c>
       <c r="F9">
-        <v>-4.885768246309785</v>
+        <v>-5.424615443259044</v>
       </c>
       <c r="G9">
-        <v>-12.37556193866483</v>
+        <v>-18.27899461047677</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.580350381510443</v>
       </c>
       <c r="E10">
-        <v>-21.60355829159584</v>
+        <v>-33.22293653146581</v>
       </c>
       <c r="F10">
-        <v>-4.832681492933976</v>
+        <v>-5.323475096846836</v>
       </c>
       <c r="G10">
-        <v>-12.79336271735747</v>
+        <v>-18.61835697843468</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.148247086218945</v>
       </c>
       <c r="E11">
-        <v>-21.69289149834515</v>
+        <v>-32.36097546766082</v>
       </c>
       <c r="F11">
-        <v>-4.470500211979767</v>
+        <v>-5.348881953458099</v>
       </c>
       <c r="G11">
-        <v>-12.19867286941049</v>
+        <v>-18.34519890017111</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.670310545831145</v>
       </c>
       <c r="E12">
-        <v>-22.38040442218967</v>
+        <v>-33.5426807599624</v>
       </c>
       <c r="F12">
-        <v>-4.245626626611397</v>
+        <v>-5.262817893776842</v>
       </c>
       <c r="G12">
-        <v>-11.98355362026865</v>
+        <v>-18.21637398632868</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.158028701958504</v>
       </c>
       <c r="E13">
-        <v>-22.4074031842234</v>
+        <v>-33.75053318844046</v>
       </c>
       <c r="F13">
-        <v>-4.542997270337975</v>
+        <v>-5.240324405321224</v>
       </c>
       <c r="G13">
-        <v>-11.70044569738679</v>
+        <v>-18.3662142432544</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.631161196371924</v>
       </c>
       <c r="E14">
-        <v>-24.0565919052848</v>
+        <v>-33.67584506663196</v>
       </c>
       <c r="F14">
-        <v>-3.895467441774018</v>
+        <v>-4.998760045153846</v>
       </c>
       <c r="G14">
-        <v>-11.80301301928449</v>
+        <v>-17.34091677119611</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.107623599235052</v>
       </c>
       <c r="E15">
-        <v>-24.68459162372051</v>
+        <v>-34.8980869940132</v>
       </c>
       <c r="F15">
-        <v>-4.148521257818225</v>
+        <v>-4.926586878450133</v>
       </c>
       <c r="G15">
-        <v>-11.55424207473596</v>
+        <v>-17.24839198919179</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.605842397433268</v>
       </c>
       <c r="E16">
-        <v>-25.05942247428341</v>
+        <v>-35.06557939789789</v>
       </c>
       <c r="F16">
-        <v>-3.872150556120018</v>
+        <v>-4.787829539909397</v>
       </c>
       <c r="G16">
-        <v>-10.75221607020997</v>
+        <v>-17.23006811963192</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.144175857669544</v>
       </c>
       <c r="E17">
-        <v>-24.21381599435711</v>
+        <v>-35.13703418926492</v>
       </c>
       <c r="F17">
-        <v>-3.437014129633854</v>
+        <v>-4.689377245719273</v>
       </c>
       <c r="G17">
-        <v>-10.7786805712509</v>
+        <v>-16.97045679371505</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.738838975058608</v>
       </c>
       <c r="E18">
-        <v>-26.07592903478517</v>
+        <v>-35.90920693468284</v>
       </c>
       <c r="F18">
-        <v>-3.388061757965417</v>
+        <v>-4.43203414326337</v>
       </c>
       <c r="G18">
-        <v>-10.08409832220195</v>
+        <v>-16.29268549491452</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.405940740668371</v>
       </c>
       <c r="E19">
-        <v>-25.53495752982887</v>
+        <v>-36.28702657809079</v>
       </c>
       <c r="F19">
-        <v>-3.279317827162912</v>
+        <v>-4.268327206917715</v>
       </c>
       <c r="G19">
-        <v>-10.3651239119396</v>
+        <v>-16.37172476966462</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.159233322434611</v>
       </c>
       <c r="E20">
-        <v>-26.89368539956429</v>
+        <v>-37.06218811635377</v>
       </c>
       <c r="F20">
-        <v>-2.998665294359634</v>
+        <v>-4.242367000881381</v>
       </c>
       <c r="G20">
-        <v>-9.922477488974732</v>
+        <v>-16.36338219490565</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.006841260612767</v>
       </c>
       <c r="E21">
-        <v>-27.68909827358956</v>
+        <v>-37.67501065415276</v>
       </c>
       <c r="F21">
-        <v>-2.759814665803828</v>
+        <v>-4.277774737146643</v>
       </c>
       <c r="G21">
-        <v>-10.51373430119749</v>
+        <v>-16.25704250636596</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.95545162327864</v>
       </c>
       <c r="E22">
-        <v>-27.43594751961278</v>
+        <v>-38.06004189241794</v>
       </c>
       <c r="F22">
-        <v>-2.959162109654931</v>
+        <v>-3.888132248422228</v>
       </c>
       <c r="G22">
-        <v>-10.36102545656199</v>
+        <v>-16.22829703944846</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.007048275596024</v>
       </c>
       <c r="E23">
-        <v>-27.66642873270717</v>
+        <v>-38.38941592089183</v>
       </c>
       <c r="F23">
-        <v>-2.408772441315064</v>
+        <v>-3.925525581352001</v>
       </c>
       <c r="G23">
-        <v>-9.957863910244001</v>
+        <v>-16.11026946988236</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.158197790244981</v>
       </c>
       <c r="E24">
-        <v>-27.7406006084788</v>
+        <v>-38.23663426482105</v>
       </c>
       <c r="F24">
-        <v>-2.696198534371034</v>
+        <v>-3.530417524503915</v>
       </c>
       <c r="G24">
-        <v>-10.10485213218764</v>
+        <v>-16.33815914844195</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.401526020184431</v>
       </c>
       <c r="E25">
-        <v>-28.08244605436982</v>
+        <v>-38.92128972156672</v>
       </c>
       <c r="F25">
-        <v>-2.604688787383772</v>
+        <v>-3.534624802542734</v>
       </c>
       <c r="G25">
-        <v>-9.923613006094701</v>
+        <v>-16.30497755050183</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.725327595296166</v>
       </c>
       <c r="E26">
-        <v>-26.80511750492227</v>
+        <v>-38.6785137015415</v>
       </c>
       <c r="F26">
-        <v>-2.448327813166143</v>
+        <v>-3.596382077523645</v>
       </c>
       <c r="G26">
-        <v>-10.01265343891894</v>
+        <v>-15.88077914255455</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.114279777371245</v>
       </c>
       <c r="E27">
-        <v>-27.37980802733969</v>
+        <v>-37.97018791115774</v>
       </c>
       <c r="F27">
-        <v>-2.361291250153999</v>
+        <v>-3.730729188011877</v>
       </c>
       <c r="G27">
-        <v>-10.3559437691592</v>
+        <v>-16.34333022057429</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.553494965885602</v>
       </c>
       <c r="E28">
-        <v>-28.06963500140212</v>
+        <v>-38.73433167216005</v>
       </c>
       <c r="F28">
-        <v>-2.209645343193105</v>
+        <v>-3.83375572700026</v>
       </c>
       <c r="G28">
-        <v>-9.895628964651243</v>
+        <v>-16.78752597885154</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.024434355063687</v>
       </c>
       <c r="E29">
-        <v>-27.97583671928124</v>
+        <v>-38.74237877047168</v>
       </c>
       <c r="F29">
-        <v>-2.554444162566968</v>
+        <v>-3.822031843148439</v>
       </c>
       <c r="G29">
-        <v>-10.47546770530905</v>
+        <v>-15.94089699427494</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.50710718685035</v>
       </c>
       <c r="E30">
-        <v>-27.71655893997208</v>
+        <v>-38.39903439968412</v>
       </c>
       <c r="F30">
-        <v>-2.816610848409373</v>
+        <v>-3.672160299164341</v>
       </c>
       <c r="G30">
-        <v>-10.72447369859087</v>
+        <v>-16.34034576377064</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.983180378750401</v>
       </c>
       <c r="E31">
-        <v>-26.55074406296341</v>
+        <v>-38.9865133326992</v>
       </c>
       <c r="F31">
-        <v>-2.524806833629608</v>
+        <v>-3.598790141563584</v>
       </c>
       <c r="G31">
-        <v>-10.41036251673374</v>
+        <v>-16.63522102077183</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.434510611230381</v>
       </c>
       <c r="E32">
-        <v>-27.34775095983939</v>
+        <v>-38.35678826566657</v>
       </c>
       <c r="F32">
-        <v>-2.50469241635483</v>
+        <v>-3.779851374997888</v>
       </c>
       <c r="G32">
-        <v>-10.68513779649325</v>
+        <v>-16.73336048801075</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.845157746687073</v>
       </c>
       <c r="E33">
-        <v>-26.55396833645688</v>
+        <v>-37.65462346417024</v>
       </c>
       <c r="F33">
-        <v>-2.479243313006024</v>
+        <v>-3.679980915814172</v>
       </c>
       <c r="G33">
-        <v>-10.92324878440533</v>
+        <v>-16.46132468468499</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.202435252206373</v>
       </c>
       <c r="E34">
-        <v>-25.91622334195666</v>
+        <v>-36.81812148123636</v>
       </c>
       <c r="F34">
-        <v>-2.595774725762247</v>
+        <v>-3.746846732568148</v>
       </c>
       <c r="G34">
-        <v>-10.85399879281486</v>
+        <v>-16.94042849040109</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.494360281773147</v>
       </c>
       <c r="E35">
-        <v>-25.78299110817699</v>
+        <v>-37.42279503005856</v>
       </c>
       <c r="F35">
-        <v>-2.656683752522692</v>
+        <v>-3.642258721025488</v>
       </c>
       <c r="G35">
-        <v>-10.67089251903777</v>
+        <v>-17.07590925605022</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.718126901574471</v>
       </c>
       <c r="E36">
-        <v>-25.85867096579318</v>
+        <v>-37.43579627893458</v>
       </c>
       <c r="F36">
-        <v>-2.563407097865259</v>
+        <v>-3.976104038232133</v>
       </c>
       <c r="G36">
-        <v>-10.5332168616961</v>
+        <v>-16.95134832486237</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.873809426827911</v>
       </c>
       <c r="E37">
-        <v>-25.98659582803586</v>
+        <v>-36.6612189138186</v>
       </c>
       <c r="F37">
-        <v>-2.706752763450103</v>
+        <v>-3.596634729581499</v>
       </c>
       <c r="G37">
-        <v>-10.20584032386311</v>
+        <v>-16.78767991921912</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.964798135087183</v>
       </c>
       <c r="E38">
-        <v>-24.91697026742412</v>
+        <v>-36.25555594797449</v>
       </c>
       <c r="F38">
-        <v>-2.437666724692114</v>
+        <v>-3.936696115778752</v>
       </c>
       <c r="G38">
-        <v>-10.60751212468842</v>
+        <v>-17.1790062652342</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.000482798960746</v>
       </c>
       <c r="E39">
-        <v>-25.07238296689336</v>
+        <v>-36.49469333913454</v>
       </c>
       <c r="F39">
-        <v>-2.817633053784427</v>
+        <v>-3.900991823983288</v>
       </c>
       <c r="G39">
-        <v>-10.46395031737793</v>
+        <v>-16.8200289149561</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.992544481547757</v>
       </c>
       <c r="E40">
-        <v>-25.07720126323752</v>
+        <v>-35.05896556160969</v>
       </c>
       <c r="F40">
-        <v>-2.736075312774399</v>
+        <v>-3.845333818189189</v>
       </c>
       <c r="G40">
-        <v>-10.76785177679194</v>
+        <v>-16.57934894370555</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.954260460424625</v>
       </c>
       <c r="E41">
-        <v>-24.57211791479201</v>
+        <v>-35.23557378367183</v>
       </c>
       <c r="F41">
-        <v>-2.696314505807426</v>
+        <v>-3.563667363684885</v>
       </c>
       <c r="G41">
-        <v>-10.63300663588635</v>
+        <v>-16.97882254229279</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.899386060750582</v>
       </c>
       <c r="E42">
-        <v>-23.6969857843357</v>
+        <v>-34.77935040553208</v>
       </c>
       <c r="F42">
-        <v>-2.74819267114255</v>
+        <v>-3.858841177059238</v>
       </c>
       <c r="G42">
-        <v>-11.10967222481277</v>
+        <v>-16.67594073090486</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.839610629871783</v>
       </c>
       <c r="E43">
-        <v>-22.81374768540567</v>
+        <v>-34.21927326873742</v>
       </c>
       <c r="F43">
-        <v>-2.990667407085605</v>
+        <v>-3.68626822440142</v>
       </c>
       <c r="G43">
-        <v>-10.28666729320441</v>
+        <v>-16.61146123543648</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.786325739719387</v>
       </c>
       <c r="E44">
-        <v>-22.8934126001486</v>
+        <v>-34.14028536085863</v>
       </c>
       <c r="F44">
-        <v>-2.870255093047266</v>
+        <v>-3.932994970223044</v>
       </c>
       <c r="G44">
-        <v>-10.77140068161004</v>
+        <v>-16.10647061887605</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.75136735998212</v>
       </c>
       <c r="E45">
-        <v>-23.2560256278388</v>
+        <v>-34.23843097802686</v>
       </c>
       <c r="F45">
-        <v>-2.8848824046459</v>
+        <v>-4.217417403076463</v>
       </c>
       <c r="G45">
-        <v>-10.16896084655563</v>
+        <v>-16.83473435824155</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.742051487515163</v>
       </c>
       <c r="E46">
-        <v>-22.40059688778987</v>
+        <v>-34.08480702579066</v>
       </c>
       <c r="F46">
-        <v>-2.932280759066685</v>
+        <v>-3.843811278902844</v>
       </c>
       <c r="G46">
-        <v>-10.15201085339456</v>
+        <v>-16.5708855340344</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.763729935851194</v>
       </c>
       <c r="E47">
-        <v>-22.50724697914452</v>
+        <v>-33.27189612819974</v>
       </c>
       <c r="F47">
-        <v>-2.947690049493561</v>
+        <v>-3.857295443485614</v>
       </c>
       <c r="G47">
-        <v>-10.15833730592011</v>
+        <v>-16.54057914489514</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.821806560730606</v>
       </c>
       <c r="E48">
-        <v>-21.09408232336289</v>
+        <v>-33.90689913168831</v>
       </c>
       <c r="F48">
-        <v>-2.805735212778018</v>
+        <v>-4.296577848822789</v>
       </c>
       <c r="G48">
-        <v>-10.3746582830927</v>
+        <v>-16.39328966330743</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.917517809532884</v>
       </c>
       <c r="E49">
-        <v>-21.23394424308978</v>
+        <v>-33.38686276206948</v>
       </c>
       <c r="F49">
-        <v>-3.231117613096217</v>
+        <v>-4.060802120066175</v>
       </c>
       <c r="G49">
-        <v>-10.60512853190015</v>
+        <v>-16.63585002442429</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.049458889824848</v>
       </c>
       <c r="E50">
-        <v>-21.33646889462344</v>
+        <v>-32.81919137436395</v>
       </c>
       <c r="F50">
-        <v>-3.298267559869354</v>
+        <v>-4.046500356856841</v>
       </c>
       <c r="G50">
-        <v>-9.974208073571383</v>
+        <v>-16.65641347804147</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.213830198933996</v>
       </c>
       <c r="E51">
-        <v>-20.96811829036553</v>
+        <v>-31.71954429531836</v>
       </c>
       <c r="F51">
-        <v>-3.526089304824288</v>
+        <v>-3.901901371391562</v>
       </c>
       <c r="G51">
-        <v>-11.14185072745449</v>
+        <v>-16.470809397655</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.401349459098261</v>
       </c>
       <c r="E52">
-        <v>-21.24474012512407</v>
+        <v>-32.17710130905337</v>
       </c>
       <c r="F52">
-        <v>-3.245448369164649</v>
+        <v>-4.309832555634984</v>
       </c>
       <c r="G52">
-        <v>-10.17960756100993</v>
+        <v>-16.72290247465219</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.608194696095794</v>
       </c>
       <c r="E53">
-        <v>-21.25035996136759</v>
+        <v>-31.58676717317646</v>
       </c>
       <c r="F53">
-        <v>-3.155649200864168</v>
+        <v>-3.847919152853327</v>
       </c>
       <c r="G53">
-        <v>-10.53017115979997</v>
+        <v>-16.46007329847115</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.826782971738705</v>
       </c>
       <c r="E54">
-        <v>-21.36184193448842</v>
+        <v>-31.02766365829345</v>
       </c>
       <c r="F54">
-        <v>-3.57898470533005</v>
+        <v>-4.173082351311231</v>
       </c>
       <c r="G54">
-        <v>-10.78275585280974</v>
+        <v>-16.34582802718367</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.046918648491708</v>
       </c>
       <c r="E55">
-        <v>-19.88715343083858</v>
+        <v>-31.75029716230445</v>
       </c>
       <c r="F55">
-        <v>-3.601556888688934</v>
+        <v>-4.289647727130968</v>
       </c>
       <c r="G55">
-        <v>-11.08931568029179</v>
+        <v>-17.25490548754031</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.263280056713034</v>
       </c>
       <c r="E56">
-        <v>-20.17269635939224</v>
+        <v>-30.92774967202521</v>
       </c>
       <c r="F56">
-        <v>-3.469020589343221</v>
+        <v>-4.16158046992336</v>
       </c>
       <c r="G56">
-        <v>-10.21393791825217</v>
+        <v>-16.26420818218571</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.468417461351779</v>
       </c>
       <c r="E57">
-        <v>-19.65362908321104</v>
+        <v>-30.99097849035731</v>
       </c>
       <c r="F57">
-        <v>-3.226856491176217</v>
+        <v>-4.219734346702093</v>
       </c>
       <c r="G57">
-        <v>-10.74617763514633</v>
+        <v>-16.47696204653974</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.655291010744493</v>
       </c>
       <c r="E58">
-        <v>-20.01277329981136</v>
+        <v>-30.56693671275307</v>
       </c>
       <c r="F58">
-        <v>-3.524478130225843</v>
+        <v>-4.180019928309676</v>
       </c>
       <c r="G58">
-        <v>-10.07924837298692</v>
+        <v>-16.71245108238472</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.818278898393192</v>
       </c>
       <c r="E59">
-        <v>-20.19610404153789</v>
+        <v>-30.74754584160098</v>
       </c>
       <c r="F59">
-        <v>-3.620745191207382</v>
+        <v>-4.363441180474557</v>
       </c>
       <c r="G59">
-        <v>-10.1672890210583</v>
+        <v>-16.66818412270635</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.95063073297389</v>
       </c>
       <c r="E60">
-        <v>-19.51325091744727</v>
+        <v>-30.7743612004374</v>
       </c>
       <c r="F60">
-        <v>-3.914979635946961</v>
+        <v>-4.225783913844738</v>
       </c>
       <c r="G60">
-        <v>-10.9672922822598</v>
+        <v>-17.18673473379563</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.05052026015299</v>
       </c>
       <c r="E61">
-        <v>-19.93113397040108</v>
+        <v>-30.23378593695677</v>
       </c>
       <c r="F61">
-        <v>-3.719986091164971</v>
+        <v>-4.176173818458478</v>
       </c>
       <c r="G61">
-        <v>-11.05846470641132</v>
+        <v>-17.02880681411747</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.11868800388022</v>
       </c>
       <c r="E62">
-        <v>-19.07724943998876</v>
+        <v>-30.6559868898769</v>
       </c>
       <c r="F62">
-        <v>-3.945512430046747</v>
+        <v>-4.42168369256539</v>
       </c>
       <c r="G62">
-        <v>-10.71581993255122</v>
+        <v>-17.44440773529927</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.15533226466598</v>
       </c>
       <c r="E63">
-        <v>-19.16857970377546</v>
+        <v>-29.87029212107209</v>
       </c>
       <c r="F63">
-        <v>-3.973210550894155</v>
+        <v>-4.356507745313125</v>
       </c>
       <c r="G63">
-        <v>-11.13841438118472</v>
+        <v>-16.92265748194628</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.16431995508457</v>
       </c>
       <c r="E64">
-        <v>-20.10133213750536</v>
+        <v>-30.54898357754966</v>
       </c>
       <c r="F64">
-        <v>-3.673933005406332</v>
+        <v>-4.425832984886013</v>
       </c>
       <c r="G64">
-        <v>-10.58930412422243</v>
+        <v>-17.01146121076446</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.15152790927413</v>
       </c>
       <c r="E65">
-        <v>-20.10140912156349</v>
+        <v>-30.25088771904674</v>
       </c>
       <c r="F65">
-        <v>-3.939578834340494</v>
+        <v>-4.363142968209549</v>
       </c>
       <c r="G65">
-        <v>-11.20639312328812</v>
+        <v>-17.66726041882085</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.12189406806536</v>
       </c>
       <c r="E66">
-        <v>-19.04712603088974</v>
+        <v>-29.36872739693053</v>
       </c>
       <c r="F66">
-        <v>-3.588614476387594</v>
+        <v>-4.547178040619904</v>
       </c>
       <c r="G66">
-        <v>-10.99354490838622</v>
+        <v>-17.69309260566378</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.08018118085885</v>
       </c>
       <c r="E67">
-        <v>-19.58171238749522</v>
+        <v>-30.31788422775322</v>
       </c>
       <c r="F67">
-        <v>-3.628999872376279</v>
+        <v>-4.673557085060608</v>
       </c>
       <c r="G67">
-        <v>-11.37539316252237</v>
+        <v>-17.26189073862817</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.02943735412646</v>
       </c>
       <c r="E68">
-        <v>-18.61463412078718</v>
+        <v>-29.92167671563712</v>
       </c>
       <c r="F68">
-        <v>-3.876396767426768</v>
+        <v>-4.589259104682119</v>
       </c>
       <c r="G68">
-        <v>-11.39375013753763</v>
+        <v>-17.22688171955037</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.970429002263751</v>
       </c>
       <c r="E69">
-        <v>-19.27984883861793</v>
+        <v>-30.00755016824457</v>
       </c>
       <c r="F69">
-        <v>-4.150128290579656</v>
+        <v>-4.573995606918135</v>
       </c>
       <c r="G69">
-        <v>-11.03384086869023</v>
+        <v>-17.91215140399735</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.907605221556562</v>
       </c>
       <c r="E70">
-        <v>-19.7829577723961</v>
+        <v>-30.01390135304033</v>
       </c>
       <c r="F70">
-        <v>-3.715425100245157</v>
+        <v>-4.563243398029798</v>
       </c>
       <c r="G70">
-        <v>-10.84838079703471</v>
+        <v>-17.11512597850843</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.842109970688162</v>
       </c>
       <c r="E71">
-        <v>-19.27532489308426</v>
+        <v>-30.03954836558277</v>
       </c>
       <c r="F71">
-        <v>-3.821399798820103</v>
+        <v>-4.722590636734519</v>
       </c>
       <c r="G71">
-        <v>-10.78894657296818</v>
+        <v>-17.25408447224657</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.772572556701988</v>
       </c>
       <c r="E72">
-        <v>-19.57562611842891</v>
+        <v>-30.400997575453</v>
       </c>
       <c r="F72">
-        <v>-3.975228453887374</v>
+        <v>-4.873536573240048</v>
       </c>
       <c r="G72">
-        <v>-11.54668078872426</v>
+        <v>-17.16644936600375</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.703020796715515</v>
       </c>
       <c r="E73">
-        <v>-19.72967121874784</v>
+        <v>-30.32891785467291</v>
       </c>
       <c r="F73">
-        <v>-4.098158176462821</v>
+        <v>-4.771797317195615</v>
       </c>
       <c r="G73">
-        <v>-10.5663719752719</v>
+        <v>-17.37191506435308</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.633061607773916</v>
       </c>
       <c r="E74">
-        <v>-20.10438432898653</v>
+        <v>-30.54417660239051</v>
       </c>
       <c r="F74">
-        <v>-3.939677410061428</v>
+        <v>-4.831651003884893</v>
       </c>
       <c r="G74">
-        <v>-10.35286165126214</v>
+        <v>-16.9720673741199</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.5612017879787</v>
       </c>
       <c r="E75">
-        <v>-20.87497663697576</v>
+        <v>-30.2470838008803</v>
       </c>
       <c r="F75">
-        <v>-3.989442410152011</v>
+        <v>-4.961109918329206</v>
       </c>
       <c r="G75">
-        <v>-11.06162296685579</v>
+        <v>-16.97482505855411</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.485606160374502</v>
       </c>
       <c r="E76">
-        <v>-21.07148523806461</v>
+        <v>-30.19493842268197</v>
       </c>
       <c r="F76">
-        <v>-4.377304737327809</v>
+        <v>-5.092435972899428</v>
       </c>
       <c r="G76">
-        <v>-9.702849276808402</v>
+        <v>-16.99642471292509</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.401646020222936</v>
       </c>
       <c r="E77">
-        <v>-20.63659323673799</v>
+        <v>-31.36564405161892</v>
       </c>
       <c r="F77">
-        <v>-4.127293514754085</v>
+        <v>-5.196495486039102</v>
       </c>
       <c r="G77">
-        <v>-9.696976369021735</v>
+        <v>-17.04362316067848</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.309485551003188</v>
       </c>
       <c r="E78">
-        <v>-21.29510128456337</v>
+        <v>-31.15349183707058</v>
       </c>
       <c r="F78">
-        <v>-4.387378513313254</v>
+        <v>-4.986737949037017</v>
       </c>
       <c r="G78">
-        <v>-10.69433780254689</v>
+        <v>-16.70596406840052</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.209104559060247</v>
       </c>
       <c r="E79">
-        <v>-21.41877390971285</v>
+        <v>-31.12295180836285</v>
       </c>
       <c r="F79">
-        <v>-4.346231019313994</v>
+        <v>-5.261481737156126</v>
       </c>
       <c r="G79">
-        <v>-10.21276598513126</v>
+        <v>-16.71367598423425</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.098916806601933</v>
       </c>
       <c r="E80">
-        <v>-21.50967396846882</v>
+        <v>-31.55682716727475</v>
       </c>
       <c r="F80">
-        <v>-4.197829827469866</v>
+        <v>-4.996988167279258</v>
       </c>
       <c r="G80">
-        <v>-10.14001343636024</v>
+        <v>-16.57877290878172</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.98242835222748</v>
       </c>
       <c r="E81">
-        <v>-21.67478665926249</v>
+        <v>-32.17634052542009</v>
       </c>
       <c r="F81">
-        <v>-4.549303631375487</v>
+        <v>-5.233867281416401</v>
       </c>
       <c r="G81">
-        <v>-9.668909563939794</v>
+        <v>-16.06733334951079</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.863095387883718</v>
       </c>
       <c r="E82">
-        <v>-22.39035800805853</v>
+        <v>-32.49594210698542</v>
       </c>
       <c r="F82">
-        <v>-4.099053641625247</v>
+        <v>-5.105399094385837</v>
       </c>
       <c r="G82">
-        <v>-10.46379141119204</v>
+        <v>-16.62852378714588</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.743839496929006</v>
       </c>
       <c r="E83">
-        <v>-23.81762886037405</v>
+        <v>-33.13893107438653</v>
       </c>
       <c r="F83">
-        <v>-4.565009477332566</v>
+        <v>-5.36331294198227</v>
       </c>
       <c r="G83">
-        <v>-9.752060536249669</v>
+        <v>-16.49400970079422</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.627511413818782</v>
       </c>
       <c r="E84">
-        <v>-24.10840670488057</v>
+        <v>-33.3446098353409</v>
       </c>
       <c r="F84">
-        <v>-4.396785453539445</v>
+        <v>-5.340149304297786</v>
       </c>
       <c r="G84">
-        <v>-9.677831484168131</v>
+        <v>-16.5147800635076</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.515727338214116</v>
       </c>
       <c r="E85">
-        <v>-24.33537382214501</v>
+        <v>-34.76520118849511</v>
       </c>
       <c r="F85">
-        <v>-4.579864589966969</v>
+        <v>-5.059972254383715</v>
       </c>
       <c r="G85">
-        <v>-9.592402856527237</v>
+        <v>-16.42006701090182</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.409829184799124</v>
       </c>
       <c r="E86">
-        <v>-26.46910020507913</v>
+        <v>-35.00875384181264</v>
       </c>
       <c r="F86">
-        <v>-4.623256959627816</v>
+        <v>-5.441051080897989</v>
       </c>
       <c r="G86">
-        <v>-9.459166640753729</v>
+        <v>-16.0103389975067</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.313301595799674</v>
       </c>
       <c r="E87">
-        <v>-26.27932091636568</v>
+        <v>-35.35649988933566</v>
       </c>
       <c r="F87">
-        <v>-4.649208881990122</v>
+        <v>-5.627206773859511</v>
       </c>
       <c r="G87">
-        <v>-9.936742629703451</v>
+        <v>-16.59183301093414</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.22664376694528</v>
       </c>
       <c r="E88">
-        <v>-28.36160383457266</v>
+        <v>-36.08413735712514</v>
       </c>
       <c r="F88">
-        <v>-4.607943759819665</v>
+        <v>-5.225761706380008</v>
       </c>
       <c r="G88">
-        <v>-9.957165385135216</v>
+        <v>-16.26458061855887</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.149442265997267</v>
       </c>
       <c r="E89">
-        <v>-28.23419974684086</v>
+        <v>-37.60712656454078</v>
       </c>
       <c r="F89">
-        <v>-4.756145315119719</v>
+        <v>-5.529987918732155</v>
       </c>
       <c r="G89">
-        <v>-10.06588370064488</v>
+        <v>-16.7974824445609</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.08436996259519</v>
       </c>
       <c r="E90">
-        <v>-29.61320159470862</v>
+        <v>-38.28003289547355</v>
       </c>
       <c r="F90">
-        <v>-4.943356348152407</v>
+        <v>-5.392999144596395</v>
       </c>
       <c r="G90">
-        <v>-9.792045305272985</v>
+        <v>-16.9866768115847</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.030802023274745</v>
       </c>
       <c r="E91">
-        <v>-31.1329008657577</v>
+        <v>-38.72020283325612</v>
       </c>
       <c r="F91">
-        <v>-4.731541146521767</v>
+        <v>-5.459600712148879</v>
       </c>
       <c r="G91">
-        <v>-9.896953182866952</v>
+        <v>-16.05795291872526</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.987757227598149</v>
       </c>
       <c r="E92">
-        <v>-31.91939943869887</v>
+        <v>-39.46682139984875</v>
       </c>
       <c r="F92">
-        <v>-5.239943356315936</v>
+        <v>-5.514979558128234</v>
       </c>
       <c r="G92">
-        <v>-9.805323903431002</v>
+        <v>-16.97852459319425</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.954424361402996</v>
       </c>
       <c r="E93">
-        <v>-33.14782046886359</v>
+        <v>-41.08893211058129</v>
       </c>
       <c r="F93">
-        <v>-4.882334663425181</v>
+        <v>-5.74260995021312</v>
       </c>
       <c r="G93">
-        <v>-11.15782742022701</v>
+        <v>-16.49047569343104</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.92694477288725</v>
       </c>
       <c r="E94">
-        <v>-34.39214323550623</v>
+        <v>-42.63103374254631</v>
       </c>
       <c r="F94">
-        <v>-5.139064774003012</v>
+        <v>-5.749517705985066</v>
       </c>
       <c r="G94">
-        <v>-10.84659641298905</v>
+        <v>-16.34045170122789</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.908052925934736</v>
       </c>
       <c r="E95">
-        <v>-36.44106941417271</v>
+        <v>-43.57819125209461</v>
       </c>
       <c r="F95">
-        <v>-5.496964223852149</v>
+        <v>-5.955488775588955</v>
       </c>
       <c r="G95">
-        <v>-10.21894015256201</v>
+        <v>-16.28220099719164</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.899484176564632</v>
       </c>
       <c r="E96">
-        <v>-38.12920074746307</v>
+        <v>-45.66466300875869</v>
       </c>
       <c r="F96">
-        <v>-5.293325836854544</v>
+        <v>-5.952466891303542</v>
       </c>
       <c r="G96">
-        <v>-10.50835466469617</v>
+        <v>-16.29013306430374</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.900444399149259</v>
       </c>
       <c r="E97">
-        <v>-40.49068220213897</v>
+        <v>-46.7131949374427</v>
       </c>
       <c r="F97">
-        <v>-5.435736275641627</v>
+        <v>-5.707738996024873</v>
       </c>
       <c r="G97">
-        <v>-10.83545973779494</v>
+        <v>-17.28024605837066</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.917608931725011</v>
       </c>
       <c r="E98">
-        <v>-41.68679030602194</v>
+        <v>-48.42132401195094</v>
       </c>
       <c r="F98">
-        <v>-5.456697284402066</v>
+        <v>-5.735008850925032</v>
       </c>
       <c r="G98">
-        <v>-11.31737585194665</v>
+        <v>-16.70260717522369</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.952161442237753</v>
       </c>
       <c r="E99">
-        <v>-43.02712804281222</v>
+        <v>-50.24811835147467</v>
       </c>
       <c r="F99">
-        <v>-5.395366618633596</v>
+        <v>-5.752072391055299</v>
       </c>
       <c r="G99">
-        <v>-11.1597740210041</v>
+        <v>-17.34936197286679</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.010390661227461</v>
       </c>
       <c r="E100">
-        <v>-45.79521891439983</v>
+        <v>-50.87555993548894</v>
       </c>
       <c r="F100">
-        <v>-5.702548445878931</v>
+        <v>-6.227354815350738</v>
       </c>
       <c r="G100">
-        <v>-12.14752163028321</v>
+        <v>-17.72136631984192</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.088308819464848</v>
       </c>
       <c r="E101">
-        <v>-47.74318729353931</v>
+        <v>-52.47136926918493</v>
       </c>
       <c r="F101">
-        <v>-5.877454081143033</v>
+        <v>-6.338513851316105</v>
       </c>
       <c r="G101">
-        <v>-11.80938250890205</v>
+        <v>-17.70508340160702</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.194354318868134</v>
       </c>
       <c r="E102">
-        <v>-50.21375515858597</v>
+        <v>-55.45004097484022</v>
       </c>
       <c r="F102">
-        <v>-6.118163566150722</v>
+        <v>-6.169968006786997</v>
       </c>
       <c r="G102">
-        <v>-12.34036090794576</v>
+        <v>-17.72732695708538</v>
       </c>
     </row>
   </sheetData>
